--- a/TPS/TPS.xlsx
+++ b/TPS/TPS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiangzhaorui/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7B38CD-8661-A64A-AD14-B9BAA96603F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97CBCFE-E2C8-4047-8B09-7FBCC3AE8EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11320" yWindow="1980" windowWidth="26960" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="900" yWindow="600" windowWidth="26960" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="107">
   <si>
     <t>Name</t>
   </si>
@@ -297,6 +297,63 @@
   </si>
   <si>
     <t>Protein</t>
+  </si>
+  <si>
+    <t>HcTC-3</t>
+  </si>
+  <si>
+    <t>PbTC-1</t>
+  </si>
+  <si>
+    <t>PcTS-1</t>
+  </si>
+  <si>
+    <t>AbTPS</t>
+  </si>
+  <si>
+    <t>AeTPS</t>
+  </si>
+  <si>
+    <t>RhTPS</t>
+  </si>
+  <si>
+    <t>AaTPS</t>
+  </si>
+  <si>
+    <t>SCB-144_TC3</t>
+  </si>
+  <si>
+    <t>NA-045_TC-3</t>
+  </si>
+  <si>
+    <t>MSCSKEVRAPRKWVQRQREMQKVKVDDNLISMDELIELVVECGLCDEASVHKMYERTNTYQFMWTLIPTVPSDQWQFEIFKTSLHFLCALFLVDDAVESYSEKQMKEMSDAYDMLEKQVCENFPCFPSINEMKQSLKHLKNPFDIASITFCMHYVNKIASVLVNEGSTPQNVVYNFRRRTSNAISISFQAVLIKAKLGSNVTGDEMLWRRVYDGLVILFYQFGELVLGLTKNTEKYMTVITELRLLGCLYCIVINDLYSYHRDKLVSSDNIIKTWLLGKAVSNLSEASSRCCEILDAVMQYMHERVERIRQSHPGCPELEALLETTVYTTVGWIFAHTAVVPRYSESPLKVHLVEVEESELHTWFCEKNHYGRSVIEKFLKAVNDEKHKGILDALSGFVDGRGQLLKTQL*</t>
+  </si>
+  <si>
+    <t>MSCSKEIHAPRRWVDRHKQIPVLPQNAVEKLISMNELIELVIECGLCDKTSINKMYDKINTYQFMWCIVDTVPASQYAEEIFKSSLHFLCALFLVDDAVESYSANEMQDLSRSYDTLEKEVCKTFPNFPSINEMKESLMHLRNPFDRSSITFCMQYVNKITAILLEEGNTPHHVVYNLRRRTSNAISIAFQAVLIKSKCGSIITSHEMLWRRVFDGLVILFYQFGELISGATETAQQHIAVVTELRMLGCLYCIVINDLYSYQRDKLASSDNMIKTWLLEKTVSSLSEATARCSQILDAIMKYMYQRVEQCIQSNPGCPQLESLLETTIYTTVGWIRSHTTVVPRYSESQLKVALVEVEEKELPKWLAEKDEYGWNVVEKFVETLNDEKHKGLLDALQGIADGRDQLLKTQLDIS*</t>
+  </si>
+  <si>
+    <t>MSCSKEIHAPRRWVERHKQVQVLPQNAVEKLISMNELIELVIECGLCDKTSIKKMYDKINTYQFMWCIVDTIPASQYAEEIFKSSLHFLCALFLVDDAVESYSANEMQDLSRSYDILEKEVCKTFPNFPSINEMKESLMHLRNPFDRSSITFCMQYVNKITAILLEEGNTPHHVVYNLRRRTSNAISIAFQAVLIKSKCGSIITSHEMLWRRVFDGLVILFYQFGELISGATETAQQHITVVTELRMLGCLYCIVINDLYSYQRDKLASSDNMIKTWLLEKTVSSLSEATARCSQILDAIMKYMYQRVEQCMQSNPGCPQLESLLETTIYTTVGWIRSHTTVVPRYSESQLKVALVEVEERELPKWLAEKDEYGWNVVEKFVETLNDEKHKGILDALQGIADGRDQLLKTQLDIS</t>
+  </si>
+  <si>
+    <t>MSCSKEIYVPRRWVQRHKKIPVLAQPAIEKLISMNELIELVIECGLCDKTSISKMHEKINTYQFMWCMVDTVPASQYAEEIFKSSLHFLCALFLVDDAVESYSAKEMQDLSRSYDILEQQVCKTFPNFPSINEMNESLVHLRKPFDRASITFCMQYVNKITAILLKEGNTPHDVVYNLRRRTSNAISIAFQAVLIKSKCGSIITSDEMLWRRVFDGLVILFYQFGELISGTTEIAQQHIPVLTELRMLGCLHCIVINDLYSYQRDKPALSDNIIKTWLLEKSVSSLLEATARCGQILDSIMKYMYQRVEQCKQSNPSCSQLKSLLETTIYTTVGWIRSHATVVPRYCESQLKVSLVEVEEGEIPKWLAKRDEYGWNVVEKFVETLNDEKHKGILNALQGIVDGRDQLLKTQLDMHDDVV*</t>
+  </si>
+  <si>
+    <t>MSCSKEIYVPRKWAQRHEKIPVLAQTTIEKLISMNELIELVIECGLCDKTCISKMYERINTYQFMWCMVDTVPASQYAEELFKISLHFLCALFLVDDAVESYSANEMWDMSRSYDALEQQVCKTYPNFPSISEMKESLVHLPNPFDRASITFCMQYVNKITAILLKEGNTPNDVVYNLRRRTSNAISIAFQAVLIKSKCGSTVTSHEMLWRRVFDGLVILFYQFDELISGTTEIAQQHIPVLTELRMLGCLYCIVINDLYSYQRDKLALSDNIVKTWLLQKSVSSLSEATARCGQILDSIMKYMYQRVEQCKQSNPSCPQLKSLLETTIFTTVGWIRSHTTVVPRYSESQLKVSLVEVEEEEIPKWLTKRDEYGWNVVETFVENLNDEKHKGLLDALQGIVDGRDQLLKTQLDMHDDIM*</t>
+  </si>
+  <si>
+    <t>MPFSKHIHVPSHWLDGQKAMLNKERDETLISMEKLIDLVTECGLCDEASIRKIDKKINTLQFMWTLVDTSPSDQWSTEIFINCSHFLCAAFLIDDAVESYSAVEMEKLSNAYDLLEQQSCEAFPNFPSICEMKKSLEGLMLNVFDIASVTFCMQYVNKIASILLKQGNTRNNLAFNVRRRTSNAISISLQAVLVKSKHGSKVAPHEMLWRRIFDGLVILFYQFGELTSGVTKHVQQHIAIVTELRMLGCLYCVVLNDLYSYHRDKFAPSDSIIKTWFTNKTVSSLSEATTKCCQILDAVLKYMYERVEECKLRFPDSPELKVLLESTVYTTVGWIFSHTIIVPRYAESPLKVILVEVEKLELAAWLAQKDEYGCNVVEEFIKTMNNKENKGIIDALSGCVEGRGQLVKTLVSDQ*</t>
+  </si>
+  <si>
+    <t>MACSKQLRVPKQWLKYHDDIFKEPVNSKLFSEDELCVWLKDLDLCHNKSVIAKYVQTTKPYHLMRHQIVLLPSNALCEKIFTLWTNTIIALFIGDDVLETLNKAEMGEICDAFQLLDEHTHDQFPQIPTIAEMRQFLMQQKVNEKFIPHVIYFQDFSNNVVKCMLEHGNSSKEDVKDFWRRLVVMIAFYYEGVEDEVKSSVGVYADDVWKRSLSSAAMVWMIAQEITSEVIGKTTVHAPLLNELYFLGTFYSMVVNDIYSYKREMLLEASVCNLVQTFTVSKVVPGESEAVQKCVDILNEVVKVMYQKIEKVKQENAGDQDLCKLFDNIGMATVGWYYFHHYSPRYDDSLWRLPIVPVEDDELKEWRQCTDKDPMEEVMALLIKYCEKAKRISDAIIGGKVNMHTNL*</t>
+  </si>
+  <si>
+    <t>MSCSKPIHVPSHWVNRQKAMLNKKTDETLISMEKLIDLVTECGLCDEASIRKIDKKINTFQFMWSLVDTSPSDQWSREMFTNCFQFLCAAFLIDDVVERYSAVEMEELSDAYDFLEQQSCEAFPNFPSISDMKKSLEGLMSNVFSIGSVTFGIQYVNKMASILLKQGSTPENVVFNARRRTSNAISISLQAILIKSKHGSNVAPHEMLWRRIFDGLVILFYEYGELVSGVTKHVQEHVAIVTELRMLGCLYAVVINDLYSYHREKHVPSESIIKTWFSQKIVSSLSEATTKCCQILDAILQYMYERVEECKLRFPECPELEVLLESTMYTTVGWIFSHEIIVPRYSESPLKVILVEVANEEVPAWLAQRDEYGWNVVEQFVKTMNNKENKGIIDALSGYVEGRGQLIKTLDK</t>
+  </si>
+  <si>
+    <t>MSCSKEIHVPRRWAERHKQIPVLPQNTVEKLVSMNELIELVIECGLCDKSSINKMYDKINTYQFMWCIVDTVPASQYAEEIFKSSLHFLCALFLVDDAVESYSANEMKDLSRSYDTLEKEVCKTFPNFPSINEMKESLMHLRNPFDRSSITFCMQYVNKITAILLKEGKTPHHVVYNLRRRTSNAISVAFQAVLIKSKCGSIITSHEMLWRRVFDGLVILFYQFGELISCATETAQKHITVVTELRMLGCLYCIVINDLYSYQRDKLTSSDNMIKTWLLEKTVSSLSEATARCSQILDAIMKYMYQRVEQCIQSNPGCPQLESLLETTIYTTVGWIRSHTTIVPRYSESLLKLAPVEVEENELPKWLAEKDEHGWNVVEKFVETLNDEKHKGILDALKGIADGRDQLLKTQLDIS</t>
+  </si>
+  <si>
+    <t>elisabethatriene</t>
   </si>
 </sst>
 </file>
@@ -358,14 +415,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -642,81 +699,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.1640625" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="11" style="1"/>
+    <col min="1" max="1" width="14.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="101.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="11" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -724,83 +782,83 @@
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -808,13 +866,13 @@
       <c r="A12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -822,13 +880,13 @@
       <c r="A13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -836,55 +894,55 @@
       <c r="A14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -892,69 +950,69 @@
       <c r="A18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -962,13 +1020,13 @@
       <c r="A23" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -976,391 +1034,377 @@
       <c r="A24" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" s="1" t="s">
+      <c r="A38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" s="1" t="s">
+      <c r="A39" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D40" s="1" t="s">
+      <c r="A40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D41" s="1" t="s">
+      <c r="A41" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D42" s="1" t="s">
+      <c r="A42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" s="1" t="s">
+      <c r="A43" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D44" s="1" t="s">
+      <c r="A44" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" s="1" t="s">
+      <c r="A45" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D46" s="1" t="s">
+      <c r="A46" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D47" s="1" t="s">
+      <c r="A47" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D48" s="1" t="s">
+      <c r="A48" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D49" s="1" t="s">
+      <c r="A49" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D51" s="1" t="s">
+      <c r="A50" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>37</v>
       </c>
     </row>

--- a/TPS/TPS.xlsx
+++ b/TPS/TPS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiangzhaorui/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiangzhaorui/Library/Caches/com.lemonmojo.RoyalTSX.App/LMFileTransferConnection/1f17b1a9-7d85-4659-ad24-11942f971285/L3NjcmF0Y2gyL216MzIvemhhb3J1aS9BcmlhZG5lL1RQUw==/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97CBCFE-E2C8-4047-8B09-7FBCC3AE8EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661D444A-F263-0B49-91BD-E792B93452C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="600" windowWidth="26960" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="900" yWindow="660" windowWidth="26960" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -98,55 +98,232 @@
     <t>Type</t>
   </si>
   <si>
+    <t>cembrene B</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>BaTC-1</t>
+  </si>
+  <si>
+    <t>MVFSKPIHAPKKWVEKGKGLLDEEVDEQLEGLQEIIDTFIQCDLCDETTVRKYRGKLRPYNFTRSLNPIIPETKLGREVFKALAHFTMGIFIADDIMEKQPEEEIRKMCTTFAHLDAKSRQSFPSFPAIDDIKEVVDASSVSKNVAGPIVFLEQFLNKQASLLLSHGDFSLSDVKEFRLRGYNMMAIYFLRVLEETEIQKKPGSIEVIWRRAFGGCVPFYLLTAEIFSGAIGKLKEHYTALTELYVLGGIYVATLNDVFSYYREAHTVADNVVKAMVSQKEVETLEEAAANVAEFLDSIMQYLYEKVEELQRKDPNNRELHVCLDYVGRMTVGSVYAHLLPRYKDTTLSYYLEEVKEDQLSSWLSKKGEYGTRMLKNILEVIHQRMADGQMEALAGAFPYCGKFLGVVIPDTICCTSSIV*</t>
+  </si>
+  <si>
+    <t>DgTC-2</t>
+  </si>
+  <si>
+    <t>MFSDNVRVPEKWTISHKKMLAEHEEDKELIALDKLLLWVKETGLTTEAASKSVFDNLNAYRYLRCLFPILPEDQTGKKLFQLNLHFLVMGYVIDDTIEKYSEKEMRELIDGYNFLQNQVSKTFPKLPSISKVWKLLGEARNKFSRSAIVTVVDYVNRTTMILLEGEICEESVLNYRNRLSNAIAVYFNAILSKTKTGCKISENEMLYRRCFDALSIAVYMSTEVFSKTLVRNQMLPTSELYKFYLLSTLFCVVINDLYSYERDKLDDTDSVIKVWYAQNEVTDMKAATTKVSKILDRIIQQMYLFVKEGKSCHPELSEWFERIAAMTVGWIYIHKYVVFRYVSSPFQIAVVEVKDEMIPDWLTEKDAYGETIVQNFLDGLEYPHQKDVLDSLYGCNRL*</t>
+  </si>
+  <si>
+    <t>ErTC-2</t>
+  </si>
+  <si>
+    <t>MSGKIVRAPSNWTTPHKKMLKEDEDQELIAFDKLLSWVSETGVGTEEQAKIVFKKINAYFYLRCLYPVLPRDPKSMKIFQLNLHFLILGYIIDDAIEKYNENEMKELIAGYNLLQSQVSETFPNFPSIFEMKQLLGNMKNDFSKSAITTMFDYVNKTTLILLEEGEIAEHNVLNYRKRLSNAVAVYFDALLSKTKTGCEISDGAMLWRRCFDALAIAVYMLTEVFSKTLVKNHTLPVSEFYKFYLLSILFCVVINDLHSYERDKLDDTDSVVKVWFKEGSVANMEAATSKVSKILDAIIQQMYLFVEEGKARHPELSEWFERIAYMTVGWIYIHKTVVPRYVSSPFQIEVVEIHENMISNWLLKKDAYGQRVVQQFLKNLNDPQKKNIMLYDE*</t>
+  </si>
+  <si>
+    <t>TmTC-1</t>
+  </si>
+  <si>
+    <t>MACGKELRIPKEWSKYHHAIVNEPIDPELFSLDELCAWLKDLDLCNDKSDVEKYVLAVRPYHTMRYQFVLLSREDALCKKLFKMWAHTAIAVFISDDVLECLSKTEMGQICNAFQLLVEKTRPQFSQFSTIAEMKQFLLLQKVDVKLMPHIIYFLDFANNVAKLINEQGNYSKEDVSDYWRRLVVMISLYYEGVKVEVSGSGGSYSKDIWTRLLAAGTMIWLIAQEVMSGALGKTSEHASLLNELYFLGTFYSMVLNDIYSHNRENGFHGSICNLLQTIVRSKDVPGEFEAVLKCIQILNTVVKLMYQKIETAKQKNLENRVLCKLLDNIGMTTTGCYFFHHYSHRYDDSAWRLSLVEVDDDELAEWQKCDDEEQLKEVMPLLLNYSQKANEISDTIKRGVVKINRHFRQ*</t>
+  </si>
+  <si>
+    <t>NA-047_TC3</t>
+  </si>
+  <si>
+    <t>MSSCNNAVRVPTQWTVPHKQVLAETENQELIAMNDLLRWVNETCLTTEEGAKIVFKKINAYFYLRCLYPIIPVDPTSLKIFQLNLHFLVLGYIIDDKLEKYNMHDMNELIGGYNDLQNQLSEMFPEFPSISEMKQSLGNIENDFSKSAIATIVDYINKSTLILLEGGKIPEDKVVNYRKRLSKSVTLYLDALLSKTKTGCEISENEMMWRRCFDALALGVYMSTEVFSETLVKNHGLPISEFYKFYFLSILFCIVINDLYSYERDRLDDTDSIIKVWYKQKTVTDMTTATSNIAKILDAIAQQMYLLVEGGKAKHPELSEWFERVASMTVGWIYIHKTVVPRYASSPYQVTLIGIEENMIPNWLLEKDGYGHRVVQEFLENLSNPWQSHPNVVDMLCS</t>
+  </si>
+  <si>
+    <t>NA-141_TC4</t>
+  </si>
+  <si>
+    <t>MSSCNNAVRVPTQWTVPHKQVLAETENQELIAMNDLLRWVNETCLTTEEGAKIVFKKINAYFYLRCLYPIIPVDPTSLKIFQLNLHFLVLGYIIDDKLEKYNMHDMNELIGGYNDLQNQLSEMFPEFPSISEMKQSLGNIENDFSKSAIATIVDYVNKSTLILLEGGKIPEDKVVNYRKRLSKSVTLYLDALLSKTKTGCEISENEMMWRRCFDALALGVYMSTEVFSETLVKNHGLPISEFYKFYFLSILFCIVINDLYSYERDRLDDTDSIIKVWYKQKTVTDMTTATSNIAKILDAIAQQMYLLVEGGKAKHPELSEWFERVASMTVGWIYIHKTVVPRYASSPYQVTLIGIEENMIPNWLLEKDGYGHRVVQEFLENLSKPWKSHPNVVDMLCS</t>
+  </si>
+  <si>
+    <t>cembrene A</t>
+  </si>
+  <si>
+    <t>Coral</t>
+  </si>
+  <si>
+    <t>Protein</t>
+  </si>
+  <si>
+    <t>CiTC-1</t>
+  </si>
+  <si>
+    <t>MSCSKEVRFPETWSKVQWNCLKTPRDEDIFGFQELIKWLEDCGASDEANVRKYEEILNVYYATRAIIPIVPENILCRELCKVKIHFFMTTFVTDDLMEEHCSFEDMRKIIAALNQLNEKLSLEFKKVPSIKEMKKYLQYMSDERAISLVTVCMDFINRCTRTLLQHGNVSDDVVFDYRKRCFITVSLWLQGVAMVKRDGAAQDTVVDVLWTRVHDGLPSAFILYTEVSSFSLGKQNAHIAELTELYCLFGLYMVAINDFYSYTREMNDTIFSQSVIKIWLKNKEINNFSEAAPKMVAILDEISKYVYRKGEKMKAENPTNFELHEMVDQIGYGVAGNYFLHHHVCKRYKDTTAIKLGIKELKGKELKQWLAEKDPYGWDIVKNFLVDHSIVAKNFVDVMRGVTPLSDDSLLNSLNK*</t>
+  </si>
+  <si>
+    <t>Sesquiterpenes</t>
+  </si>
+  <si>
+    <t>DgTC-1</t>
+  </si>
+  <si>
+    <t>MWCGKEVRVPRQWAVLEQEVLKEKPDPELVDIDGMIKWITECDIVDENVVRAYVKLVKPYYFIRLIYPILPKDKLCVEACKIFLHFVISLYCSDDRTELECDLDDIVKMCDAYENLKEPVFEMFPKFPTIKEMQSSLKFLSDSKLISPVVLCMDFVNKVTSCVIEYGEYSETAVLDFRRRFLNTIEFYLRGLEMEKKMHRKDTENKTLWRRIFDGGPLFFLPYVEISSFSLGKVEGHIPTISEMYIVSAFVCIIVNDLYSYKRETMESINCDSVIKHWLSDEKISSMEEACEKVSRILNATVQYMFEKVQRVKLDYPNSPEAHVLYEYIAHVTIGWLYMHEEGNDRYKDSPWRVSLTEVEEDKIQEWLSCKDSYGFEALNQFLASNPKAEKIIDALGGDEIIHGGLINESS*</t>
+  </si>
+  <si>
+    <t>HcTC-2</t>
+  </si>
+  <si>
+    <t>MACSKEMYIPKEWTKYHHDIVKEVKRADLEADDEVAKWVVGLGLSDKPATEKYIDSTRPYHFMRCIAVLVPSNPLCRNIFKTWQIYVTGLFVSDDYLEQTSLAEVVQVSDSFDMLNEQISERFPVIPTHAQIMRSLKINEKLIPHVLVQIDWLNTIANDLLQHGDFSEDDVWDFRCRMSAWIRAYFDGLKSQVGPKVKVTTDDFMWLRIIDGGVGPFLLINEILVGELGKCKGHVKLITQLYILSSCVCVLINDCYSYHRETVVTIYNTIKVILENKEVSEVPDAVSKLLQTINAIIKYMYQTIEKTKHEYPDNLMLNKLLDAIGGATAGWFFVHDKVLPRYQATSWRFSLVEVEEMELKEWRKSADEKPSDLVQPLLYRFNAKGKEIIDALAYVPKRSRRIVPE*</t>
+  </si>
+  <si>
+    <t>TmTC-2</t>
+  </si>
+  <si>
+    <t>MSCSKEIRIPSDWASVQRKSMQEGPDESLLDFEELANWLRECGVTDDQCKVRKYVDATRPVLSIRTILRVFPNNTLCRMHFKFLTQYTIGIYIDDDVLESHYPLEVLKEICYEYDQLDGKLLGQFPQIPSRKELKNFLAHLKNEKVISTVTFHMDFVNRVTVNILQNGDFSEEAVLEFRRRLSNNILLYLQGVQYEKRGAGGKPSTVVEALWNRVFGGAAVTWRLFGEVPSGTLGKIGEHITLISELYILSALYCIVINDLYSYHREIDAVPTAGENFVRVMFNQKEVANLTVAAGKVASILNEITKYTYEQVREFKASYPNSSELHQLFDDIGCGTVGWYYFHECTNPRYKESNVRISMKDVDKNEIEDWLSTKDSYGWNIVKQFLASYDAKAKRLNDAVACRIPAYAETF*</t>
+  </si>
+  <si>
+    <t>PcTS-2</t>
+  </si>
+  <si>
+    <t>MSCSNEVRIPSNWAFLEKEVLKEQPDPELVDIDGLIKWVVECEIADENMVRKYVKIVRPYYFARLLYPILPNNRLCREAFKIFLHFVIAVYRCDDRMETECDLNDMGKICNAYDKLDEQLCETFPKIPTVKEMQSSLKFLSEAKLIAPVTLCMDFVNKVTCAILTHGSVSEDVVFEFRRRLSNSVSIYLKAVKSEKNMTPEDSDNETLWRRIFGGGPLFLLLYVEISSFSLGKTKEFIPTITEMYVVSSLCCIITNDVYSYYRETTESLIYCDSIIKVWLHNKEITTIPEAIARITNILNATVKYMFEMGKNVKIQYPNSPEVHALFEYIAYATIGWMFMHDQGSHRYRDSPWRISLVDVKEIDLQQNKDSYGEDVLKTFLEMSNSKAKKIIDALRGVIAVREDLIYDNC</t>
+  </si>
+  <si>
+    <t>NA-218_TC-2</t>
+  </si>
+  <si>
+    <t>MWRTDVVKVPRKWVQPHKELLKNKRNHEHLIVEEMYQEVYEIGLTTEEKVREIIVNINAGTYARFLFPDFLDNPESNKVPQLMIYYVTVLYLIDDQLETFNETEIEELIDGYNQLEREMFETFPKCANMTKMKTMLRNVKNEFTKSSIVMMMDIVFKATSLYLEQRQPPHEKMLDFRNRFSAQLSLFNYAHLSRAKYGTNATPGEMMWRRCTDSLMFALPMAIEMLDKTSEKEVPTMREIYELYTMSVLYGVVINDLYSYFREQFDCSNNLLKVLFPKKVDPNMTDATVKICQILNAIMKHAYFLVEKLKLKYPHAKNLLDDNAYQISSWIYIHATVAPRYYTSPCHVEVVEIEDGELSDWLTQENEYGSRVFQEFLDIMNDPTQKSARDFFHGTDVDRQFSI</t>
+  </si>
+  <si>
+    <t>SCB-144_TC4</t>
+  </si>
+  <si>
+    <t>MAYSKPIHAPREWVKDVKEVLTPALVDEELLGLDELVAWALECGICNEKLVKKYAKYISPYLLIRGLYPVLPNNTLCRSVFTIFVHFTLLLYIADDRMEKQSEEEGRNMCVGFTLLDEQSRKSFPEFPTVEEMKATIIHMSTPSIVGRTVMLASFVDKLASALLKHGNYSDDVVYDYRLRASNMLSIYIQALLAEKHQQKQGTVLEAFWRRHFGGCVIIFHLLADIFSGALGKTKHHLAVITDLYINCTLLCIAINDLFSYFLEKESSCDNIFREILAEKEEENIPEAVHKMSQIADAILKRLYRTMQETLQQYPKHQELRSLMGYVGRCAVGWFWMHSILQRYMDSPFKFTLDEVDDEHLMTWSSKNNDYGENVVNDLMKMFKERMADGKMDALKGAFPIHEKISGYKEDGLYNVV</t>
+  </si>
+  <si>
+    <t>SCB-157_TC5</t>
+  </si>
+  <si>
+    <t>MAYSKPIHAPSVWVKHVKEVFTPASSVDEELLGLDELVGWALECEICDEEMVKKYVKSITPYRFMRALYPVFPDNILCRSVFKVLAHYVILLYIADDKMEQQSEEEMRNMCVGFTLFDEQSRKSFPELPTVEEMKMTINHLSTPGTVGCTVMFASVANKMASALLKHGNYPDDVVYDYRLRASNMLSIYIQAILAEKHQQKHGTVLETYWRRQFGGCVLIYHLLADISSGALGKTKQHLGVITEMYIYCTLLCIAINDLYSYSFEKETICDNIFKAILEEKQEENIPEAVDKISQIADAILKRLYRKIQETLQKYPNNQELRSLMDYLGRCAIGWFWLHSILQRYKDTPFKLTLVEVDDEHLMTWSSKNDDYGENVVNDIMKMIKERMADGKMDAMMGAFPIHEKISAYKEDGLYNVV</t>
+  </si>
+  <si>
+    <t>NA-195_TC-1</t>
+  </si>
+  <si>
+    <t>MSCSKEIRMPKKWSKYHHDIMKKTVNEEIFNEDECMNWFAACGVSDKSCIKKYIEAIRPYHFTLCLAGFIATSHRDVMRSYMYYLIGVYYVDDCLESHSSSEVHQVGEAYAKLEKQVWEQYPQFSTIPEMKQYLKERVEIDETLIHHVVILFESLSKITNALLQHGQLNQNDVRNFSRRLSNSITMFLEAVEAESTPSITANSTYHEILWRRIEGGAPMMFINVVEITAESIGKVKEHTTCITELYVLSSLFVIFLNDLYSSYKEKIEKIDCDNVVHSLIANKDALHVLDAAEKITPIMNGIIKLMYQKIEKIKCEYPNNPDLHKLLDYIGVGTAGWYTIHAECSPRYFASTSCRIPLVEVEEKELEQWKKDHDQLSFDEPGVSIESYLYHSNTKAKTMIDAHSGRISPRGHFIPV</t>
+  </si>
+  <si>
+    <t>SCB-157_TC2</t>
+  </si>
+  <si>
+    <t>MAYSKPEVHFPKEWTKHHHVIGKETVNEELFPEDELVDWLTSIDMCEKSTIQKYIEMCRPYHFIRCLAVLVPIHLSSCRDLFKIYVQFVIAIFISDDLLETYNSTELRQIRDSYEMLEGQVSAESFLPFPTIAKMKASLKIKKKLMPNVIYLVDCTNMVAHSLIQQGTISEDDVAYFRKRISIAHSMYLEAVEAEMSPRVDETITEILWRRIFNGALPGILLGVEAMSGMVGKVKPHALLIAEMEILCSLYCILINDIYSYGKELLSKVGNKDTKCDNIVVSMLHNKEVSSISEAVQKIFPVCNEVTKYMYQKIEKSKQEYPDNEDLHKLLDHIGRATAGWFFIHDSVLPRYEDTPCVISLVEVEEMELKEWRESKDEEQSVILKRFFDHTSPKGKILMDAMCGLIKTRGHFVPT</t>
+  </si>
+  <si>
+    <t>NA-047_TC4</t>
+  </si>
+  <si>
+    <t>MACSKELRIPKPWLKYHDAIVKEPVDPKLFSLDELCAWLKDLDLCHNKSDVAKYVLQTRPYHLVRHQVVLLPDNALCRELFTLWVNTAVALYISDDVLELLSDIEMRQICDACQLLDDHIREQFPQFPTIAEMKQFLLVQKLDEKLIPHVIYFQDFSNNVAKAIMEHSNFSKEEVKYFWRRLVVKIALYYEGVGDEGKHTIGLYSKNVWTRLLAAGVMIWVFSLEIMFGVVGKTTQHLPLLNELYFIATFLAMVVNDIYSYKREMGLDARVCNIVQTIIVGEEASGESQAVQKCVEMLNAVVKVSYQKIERAKQENPGDQDLWKLLDNIGMATVGWYFCQHFSPRYDDSPWRLSIVEVEGAELEEWRHTDEDPPKEVIPLLVSYNAKAKRISDAIISGDVNMHGNL</t>
+  </si>
+  <si>
+    <t>SCB-084_TC1</t>
+  </si>
+  <si>
+    <t>MSCSKEVQFPSNWAKVQWHYLRKPKDEGLIGLEELINWAEECGIADEITVRKYVEVVKPYKTYRSVCPIVPDNTLCRGLFKTCMQFMLVLFILDDVFEKNCNLDDMEKIINAYHQLDEKLSETFPKVPSIKELQPYLQYLSDKRINSIITFLMDYVNRSVRVLLQHGNVSDDAVLDYRQRLSNGMSLYLQGIASEKRDTTQDSENKVLWRRMFDGALHILISYIEASSFSLGKQKAHITAITELYTLFSLYCVVINDLYSYTRESNESVPSTNVIKVWLNKKEIANISESARKVVSILDEITKYVYKRVEKMKVENPNNSELHELLDQIGYAIAGNYFFHHYASDRYKDAQIKLGMKEVEENELQEWLAERDPYGWDVVKQFLNEHSTVAKNFTEILCGVTPRSVDSLLSLLSK</t>
+  </si>
+  <si>
+    <t>SCB-084_TC6</t>
+  </si>
+  <si>
+    <t>MSCSKEVQFPSNWAKVQWHYLRKPKDESLLGLEELIKWVEECGTGDEITVRKYVEKLKPYEGMRAFCPIVPDNNVCRGVFKIYVQYILGVFIIDDVMEKNYNLDYMMKIINAYDQLDEKLSEIFPKVPSIKELQPFLQYLSDKRIRSIVTFYMDFVNRCTRVLLQDGNVSDDAIFDFRQRLAIGISLYLQGAASEKRNTTQHTEIEVLWRRVFDGMPIPFVQYVEVSSFSLGKQKAHVAAITELYTLFSLYCVVINDLYSYTREDNESVPAASVIKLWLDKKKIGNISESVPKIISILDEIAKYVYKRVEKMKVENPNNSELHELLDQIGYSIAGNYFFHHHASDRYKDAEVKLGMREVEENELQEWLADNDPYGWDVVKQFLYEHSTVAKNFIDISCGVTPRSVDSLLSLLSK</t>
+  </si>
+  <si>
+    <t>SCB-084_TC2</t>
+  </si>
+  <si>
+    <t>MSCSKAVRFPSNWARVQWHYLRKPKDEGLIGLEELIKWLRDECGAADESTILKYVKNVKPYESMRAFCPIVPDNNVCRVVFKIYVHFILGLFIIDDVMEKDCNPDDMEKIVNAFDQLDKKLSEAFPKILSIKEMQPFLQYLSDKRASSIVTFFLDFLNRCARVLLQDGSVSDDAIFDYRQRLAHAISLYLQGAASEKRDATQDTLHKVLWRRLHDGAPIPFLQYVEVSSFSLGKINKAHIAAATELYVLFALYCVLINDIYSYTRESNESLPTTNLVLVWLKKKEIGNLSESIPKIISILDEIAKYVYKRVEKIKAENPNNSELHELFDEIGYGIAGNYFFHEHASDRYKDSEVKLAIKELEENDLQDWLADSDPYASDVVKQFLLEHSTVSVAKNFNDLLCGVTPLSVDSVLSLLNE</t>
+  </si>
+  <si>
+    <t>NA-045_TC-1</t>
+  </si>
+  <si>
+    <t>MSCSNEVRIPSDWAFLEKEVLKEQPDPELVDIDGLIKWVVECEIADESMVRKYVKIVRPYYFARLLYPILPNNRLCREAFKVFLHFVIAVYRCDDRMETECDRDDMEKICNAYDKLDERLCETFPKIPTVKEMQSSLKFLSEAKLIAPVTLCMDFVNKVTCAILTHGSVSEQVVFEFRRRLSNSVSIYLKAVKSEKNMTPEDSDNETLWRRIFGGGPLFLLLYVEISSFSLGKTNAFIPTITEMYVVSSLCCIITNDVYSYYRETTESLIYCDSIIKVWLHNKEITTIPEAIARITNILNATVKYMFDMVKNVKIQYPNSPEVHALFEYIAYATIGWMFMHDQGSHRYKDSPWRISLVDVKEQDLQQNKDSYGEDVLKTFLGMSNSKAKNIIDALRGVISVREDLIYDNQ</t>
+  </si>
+  <si>
+    <t>HcTC-3</t>
+  </si>
+  <si>
+    <t>MSCSKEVRAPRKWVQRQREMQKVKVDDNLISMDELIELVVECGLCDEASVHKMYERTNTYQFMWTLIPTVPSDQWQFEIFKTSLHFLCALFLVDDAVESYSEKQMKEMSDAYDMLEKQVCENFPCFPSINEMKQSLKHLKNPFDIASITFCMHYVNKIASVLVNEGSTPQNVVYNFRRRTSNAISISFQAVLIKAKLGSNVTGDEMLWRRVYDGLVILFYQFGELVLGLTKNTEKYMTVITELRLLGCLYCIVINDLYSYHRDKLVSSDNIIKTWLLGKAVSNLSEASSRCCEILDAVMQYMHERVERIRQSHPGCPELEALLETTVYTTVGWIFAHTAVVPRYSESPLKVHLVEVEESELHTWFCEKNHYGRSVIEKFLKAVNDEKHKGILDALSGFVDGRGQLLKTQL*</t>
+  </si>
+  <si>
+    <t>elisabethatriene</t>
+  </si>
+  <si>
+    <t>PbTC-1</t>
+  </si>
+  <si>
+    <t>MSCSKEIHAPRRWVDRHKQIPVLPQNAVEKLISMNELIELVIECGLCDKTSINKMYDKINTYQFMWCIVDTVPASQYAEEIFKSSLHFLCALFLVDDAVESYSANEMQDLSRSYDTLEKEVCKTFPNFPSINEMKESLMHLRNPFDRSSITFCMQYVNKITAILLEEGNTPHHVVYNLRRRTSNAISIAFQAVLIKSKCGSIITSHEMLWRRVFDGLVILFYQFGELISGATETAQQHIAVVTELRMLGCLYCIVINDLYSYQRDKLASSDNMIKTWLLEKTVSSLSEATARCSQILDAIMKYMYQRVEQCIQSNPGCPQLESLLETTIYTTVGWIRSHTTVVPRYSESQLKVALVEVEEKELPKWLAEKDEYGWNVVEKFVETLNDEKHKGLLDALQGIADGRDQLLKTQLDIS*</t>
+  </si>
+  <si>
+    <t>PcTS-1</t>
+  </si>
+  <si>
+    <t>MSCSKEIHAPRRWVERHKQVQVLPQNAVEKLISMNELIELVIECGLCDKTSIKKMYDKINTYQFMWCIVDTIPASQYAEEIFKSSLHFLCALFLVDDAVESYSANEMQDLSRSYDILEKEVCKTFPNFPSINEMKESLMHLRNPFDRSSITFCMQYVNKITAILLEEGNTPHHVVYNLRRRTSNAISIAFQAVLIKSKCGSIITSHEMLWRRVFDGLVILFYQFGELISGATETAQQHITVVTELRMLGCLYCIVINDLYSYQRDKLASSDNMIKTWLLEKTVSSLSEATARCSQILDAIMKYMYQRVEQCMQSNPGCPQLESLLETTIYTTVGWIRSHTTVVPRYSESQLKVALVEVEERELPKWLAEKDEYGWNVVEKFVETLNDEKHKGILDALQGIADGRDQLLKTQLDIS</t>
+  </si>
+  <si>
+    <t>AbTPS</t>
+  </si>
+  <si>
+    <t>MSCSKEIYVPRRWVQRHKKIPVLAQPAIEKLISMNELIELVIECGLCDKTSISKMHEKINTYQFMWCMVDTVPASQYAEEIFKSSLHFLCALFLVDDAVESYSAKEMQDLSRSYDILEQQVCKTFPNFPSINEMNESLVHLRKPFDRASITFCMQYVNKITAILLKEGNTPHDVVYNLRRRTSNAISIAFQAVLIKSKCGSIITSDEMLWRRVFDGLVILFYQFGELISGTTEIAQQHIPVLTELRMLGCLHCIVINDLYSYQRDKPALSDNIIKTWLLEKSVSSLLEATARCGQILDSIMKYMYQRVEQCKQSNPSCSQLKSLLETTIYTTVGWIRSHATVVPRYCESQLKVSLVEVEEGEIPKWLAKRDEYGWNVVEKFVETLNDEKHKGILNALQGIVDGRDQLLKTQLDMHDDVV*</t>
+  </si>
+  <si>
+    <t>AeTPS</t>
+  </si>
+  <si>
+    <t>MSCSKEIYVPRKWAQRHEKIPVLAQTTIEKLISMNELIELVIECGLCDKTCISKMYERINTYQFMWCMVDTVPASQYAEELFKISLHFLCALFLVDDAVESYSANEMWDMSRSYDALEQQVCKTYPNFPSISEMKESLVHLPNPFDRASITFCMQYVNKITAILLKEGNTPNDVVYNLRRRTSNAISIAFQAVLIKSKCGSTVTSHEMLWRRVFDGLVILFYQFDELISGTTEIAQQHIPVLTELRMLGCLYCIVINDLYSYQRDKLALSDNIVKTWLLQKSVSSLSEATARCGQILDSIMKYMYQRVEQCKQSNPSCPQLKSLLETTIFTTVGWIRSHTTVVPRYSESQLKVSLVEVEEEEIPKWLTKRDEYGWNVVETFVENLNDEKHKGLLDALQGIVDGRDQLLKTQLDMHDDIM*</t>
+  </si>
+  <si>
+    <t>RhTPS</t>
+  </si>
+  <si>
+    <t>MPFSKHIHVPSHWLDGQKAMLNKERDETLISMEKLIDLVTECGLCDEASIRKIDKKINTLQFMWTLVDTSPSDQWSTEIFINCSHFLCAAFLIDDAVESYSAVEMEKLSNAYDLLEQQSCEAFPNFPSICEMKKSLEGLMLNVFDIASVTFCMQYVNKIASILLKQGNTRNNLAFNVRRRTSNAISISLQAVLVKSKHGSKVAPHEMLWRRIFDGLVILFYQFGELTSGVTKHVQQHIAIVTELRMLGCLYCVVLNDLYSYHRDKFAPSDSIIKTWFTNKTVSSLSEATTKCCQILDAVLKYMYERVEECKLRFPDSPELKVLLESTVYTTVGWIFSHTIIVPRYAESPLKVILVEVEKLELAAWLAQKDEYGCNVVEEFIKTMNNKENKGIIDALSGCVEGRGQLVKTLVSDQ*</t>
+  </si>
+  <si>
+    <t>AaTPS</t>
+  </si>
+  <si>
+    <t>MACSKQLRVPKQWLKYHDDIFKEPVNSKLFSEDELCVWLKDLDLCHNKSVIAKYVQTTKPYHLMRHQIVLLPSNALCEKIFTLWTNTIIALFIGDDVLETLNKAEMGEICDAFQLLDEHTHDQFPQIPTIAEMRQFLMQQKVNEKFIPHVIYFQDFSNNVVKCMLEHGNSSKEDVKDFWRRLVVMIAFYYEGVEDEVKSSVGVYADDVWKRSLSSAAMVWMIAQEITSEVIGKTTVHAPLLNELYFLGTFYSMVVNDIYSYKREMLLEASVCNLVQTFTVSKVVPGESEAVQKCVDILNEVVKVMYQKIEKVKQENAGDQDLCKLFDNIGMATVGWYYFHHYSPRYDDSLWRLPIVPVEDDELKEWRQCTDKDPMEEVMALLIKYCEKAKRISDAIIGGKVNMHTNL*</t>
+  </si>
+  <si>
+    <t>SCB-144_TC3</t>
+  </si>
+  <si>
+    <t>MSCSKPIHVPSHWVNRQKAMLNKKTDETLISMEKLIDLVTECGLCDEASIRKIDKKINTFQFMWSLVDTSPSDQWSREMFTNCFQFLCAAFLIDDVVERYSAVEMEELSDAYDFLEQQSCEAFPNFPSISDMKKSLEGLMSNVFSIGSVTFGIQYVNKMASILLKQGSTPENVVFNARRRTSNAISISLQAILIKSKHGSNVAPHEMLWRRIFDGLVILFYEYGELVSGVTKHVQEHVAIVTELRMLGCLYAVVINDLYSYHREKHVPSESIIKTWFSQKIVSSLSEATTKCCQILDAILQYMYERVEECKLRFPECPELEVLLESTMYTTVGWIFSHEIIVPRYSESPLKVILVEVANEEVPAWLAQRDEYGWNVVEQFVKTMNNKENKGIIDALSGYVEGRGQLIKTLDK</t>
+  </si>
+  <si>
+    <t>NA-045_TC-3</t>
+  </si>
+  <si>
+    <t>MSCSKEIHVPRRWAERHKQIPVLPQNTVEKLVSMNELIELVIECGLCDKSSINKMYDKINTYQFMWCIVDTVPASQYAEEIFKSSLHFLCALFLVDDAVESYSANEMKDLSRSYDTLEKEVCKTFPNFPSINEMKESLMHLRNPFDRSSITFCMQYVNKITAILLKEGKTPHHVVYNLRRRTSNAISVAFQAVLIKSKCGSIITSHEMLWRRVFDGLVILFYQFGELISCATETAQKHITVVTELRMLGCLYCIVINDLYSYQRDKLTSSDNMIKTWLLEKTVSSLSEATARCSQILDAIMKYMYQRVEQCIQSNPGCPQLESLLETTIYTTVGWIRSHTTIVPRYSESLLKLAPVEVEENELPKWLAEKDEHGWNVVEKFVETLNDEKHKGILDALKGIADGRDQLLKTQLDIS</t>
+  </si>
+  <si>
+    <t>XsTC-1</t>
+  </si>
+  <si>
+    <t>MSEKNVVRIPMKWGRIEREILTQNTIPELVDTNRLISWVKECNLADEALVTKYMNVIRPYHFSRLVFPILPDKDVCREAFAVFIEFLIVLYLCDDELEAKCNLNELEIVCSAYDFLDEKLKQCFPRIPSVEELRSFLPHVKKERLLALVVSLIDSVSRVVSPLLKYSVFPQESVFDFRCRFSHSLGYNLKGVLHEKKMLGGVSENKLLWRRIFEGAPITFLMYLEISSLSVTGSNKHIPIATEMYILSSLCCMVTNDVYSYHRECNEGLKVDNIISLWLHNKQIASVAEGVSRISRILNSAVKYMLAKVKSMKSEYPNNFNVQTLTEFIALSSVGWLYMHDQGVPRYSDSPWRLNLVDIEESDITSWLAEKDPYADGVIDQFKYSNLDAKKFIDSLCEKTSVSEEQWND*</t>
+  </si>
+  <si>
     <t>xeniaphyllene</t>
   </si>
   <si>
-    <t>cembrene B</t>
-  </si>
-  <si>
-    <t>Species</t>
-  </si>
-  <si>
-    <t>BaTC-1</t>
-  </si>
-  <si>
-    <t>MVFSKPIHAPKKWVEKGKGLLDEEVDEQLEGLQEIIDTFIQCDLCDETTVRKYRGKLRPYNFTRSLNPIIPETKLGREVFKALAHFTMGIFIADDIMEKQPEEEIRKMCTTFAHLDAKSRQSFPSFPAIDDIKEVVDASSVSKNVAGPIVFLEQFLNKQASLLLSHGDFSLSDVKEFRLRGYNMMAIYFLRVLEETEIQKKPGSIEVIWRRAFGGCVPFYLLTAEIFSGAIGKLKEHYTALTELYVLGGIYVATLNDVFSYYREAHTVADNVVKAMVSQKEVETLEEAAANVAEFLDSIMQYLYEKVEELQRKDPNNRELHVCLDYVGRMTVGSVYAHLLPRYKDTTLSYYLEEVKEDQLSSWLSKKGEYGTRMLKNILEVIHQRMADGQMEALAGAFPYCGKFLGVVIPDTICCTSSIV*</t>
-  </si>
-  <si>
-    <t>DgTC-2</t>
-  </si>
-  <si>
-    <t>MFSDNVRVPEKWTISHKKMLAEHEEDKELIALDKLLLWVKETGLTTEAASKSVFDNLNAYRYLRCLFPILPEDQTGKKLFQLNLHFLVMGYVIDDTIEKYSEKEMRELIDGYNFLQNQVSKTFPKLPSISKVWKLLGEARNKFSRSAIVTVVDYVNRTTMILLEGEICEESVLNYRNRLSNAIAVYFNAILSKTKTGCKISENEMLYRRCFDALSIAVYMSTEVFSKTLVRNQMLPTSELYKFYLLSTLFCVVINDLYSYERDKLDDTDSVIKVWYAQNEVTDMKAATTKVSKILDRIIQQMYLFVKEGKSCHPELSEWFERIAAMTVGWIYIHKYVVFRYVSSPFQIAVVEVKDEMIPDWLTEKDAYGETIVQNFLDGLEYPHQKDVLDSLYGCNRL*</t>
-  </si>
-  <si>
-    <t>ErTC-2</t>
-  </si>
-  <si>
-    <t>MSGKIVRAPSNWTTPHKKMLKEDEDQELIAFDKLLSWVSETGVGTEEQAKIVFKKINAYFYLRCLYPVLPRDPKSMKIFQLNLHFLILGYIIDDAIEKYNENEMKELIAGYNLLQSQVSETFPNFPSIFEMKQLLGNMKNDFSKSAITTMFDYVNKTTLILLEEGEIAEHNVLNYRKRLSNAVAVYFDALLSKTKTGCEISDGAMLWRRCFDALAIAVYMLTEVFSKTLVKNHTLPVSEFYKFYLLSILFCVVINDLHSYERDKLDDTDSVVKVWFKEGSVANMEAATSKVSKILDAIIQQMYLFVEEGKARHPELSEWFERIAYMTVGWIYIHKTVVPRYVSSPFQIEVVEIHENMISNWLLKKDAYGQRVVQQFLKNLNDPQKKNIMLYDE*</t>
-  </si>
-  <si>
-    <t>TmTC-1</t>
-  </si>
-  <si>
-    <t>MACGKELRIPKEWSKYHHAIVNEPIDPELFSLDELCAWLKDLDLCNDKSDVEKYVLAVRPYHTMRYQFVLLSREDALCKKLFKMWAHTAIAVFISDDVLECLSKTEMGQICNAFQLLVEKTRPQFSQFSTIAEMKQFLLLQKVDVKLMPHIIYFLDFANNVAKLINEQGNYSKEDVSDYWRRLVVMISLYYEGVKVEVSGSGGSYSKDIWTRLLAAGTMIWLIAQEVMSGALGKTSEHASLLNELYFLGTFYSMVLNDIYSHNRENGFHGSICNLLQTIVRSKDVPGEFEAVLKCIQILNTVVKLMYQKIETAKQKNLENRVLCKLLDNIGMTTTGCYFFHHYSHRYDDSAWRLSLVEVDDDELAEWQKCDDEEQLKEVMPLLLNYSQKANEISDTIKRGVVKINRHFRQ*</t>
-  </si>
-  <si>
-    <t>NA-047_TC3</t>
-  </si>
-  <si>
-    <t>MSSCNNAVRVPTQWTVPHKQVLAETENQELIAMNDLLRWVNETCLTTEEGAKIVFKKINAYFYLRCLYPIIPVDPTSLKIFQLNLHFLVLGYIIDDKLEKYNMHDMNELIGGYNDLQNQLSEMFPEFPSISEMKQSLGNIENDFSKSAIATIVDYINKSTLILLEGGKIPEDKVVNYRKRLSKSVTLYLDALLSKTKTGCEISENEMMWRRCFDALALGVYMSTEVFSETLVKNHGLPISEFYKFYFLSILFCIVINDLYSYERDRLDDTDSIIKVWYKQKTVTDMTTATSNIAKILDAIAQQMYLLVEGGKAKHPELSEWFERVASMTVGWIYIHKTVVPRYASSPYQVTLIGIEENMIPNWLLEKDGYGHRVVQEFLENLSNPWQSHPNVVDMLCS</t>
-  </si>
-  <si>
-    <t>NA-141_TC4</t>
-  </si>
-  <si>
-    <t>MSSCNNAVRVPTQWTVPHKQVLAETENQELIAMNDLLRWVNETCLTTEEGAKIVFKKINAYFYLRCLYPIIPVDPTSLKIFQLNLHFLVLGYIIDDKLEKYNMHDMNELIGGYNDLQNQLSEMFPEFPSISEMKQSLGNIENDFSKSAIATIVDYVNKSTLILLEGGKIPEDKVVNYRKRLSKSVTLYLDALLSKTKTGCEISENEMMWRRCFDALALGVYMSTEVFSETLVKNHGLPISEFYKFYFLSILFCIVINDLYSYERDRLDDTDSIIKVWYKQKTVTDMTTATSNIAKILDAIAQQMYLLVEGGKAKHPELSEWFERVASMTVGWIYIHKTVVPRYASSPYQVTLIGIEENMIPNWLLEKDGYGHRVVQEFLENLSKPWKSHPNVVDMLCS</t>
-  </si>
-  <si>
-    <t>cembrene A</t>
-  </si>
-  <si>
-    <t>Coral</t>
+    <t>NA-045_TC-5</t>
+  </si>
+  <si>
+    <t>MACSKHIRIPATWLYPHQKILQDAPKADSEAPKEMVDWLCYEVKLADEALVNHTFHHLKPYLFVSLMYPRLPSDPWSKKLFELNVYFLVAAYILDDYHMENYPTTLIEKMLAAFNSVNKDMDECFPNCPTGTEIVQSLSYVENPSARYIIATMTDYINRSALIVWNSGRVQLSRAQDFRKRMAGTLRAYFHGVQMKGRHWTALSVSQFLWERCPESGAPCYYLSNEFFSGFLETTSSFPLAMLYDHYMYGSAVCSVVNDLVSLDRDTSSGDVNIIKILDKTGKIEDMEVAKSAILQLLESLVRYIYNSTKQMKEEYPECSSWFDFINDMTTGWICIHMFSPRYASSPNKVFMTPLHGEALDEWLNEKENASTFTDILAFQKLLDEMRDKMKMLYAF</t>
+  </si>
+  <si>
+    <t>NA-195_TC-3</t>
+  </si>
+  <si>
+    <t>MACSKHVRIPATWLYPHAEVLRDPPKEDSTTPKELVTWLSHEVKLADEDMVDKTFHHLKPFFFVSLMYPRMPTDPWCLKLYELNVYFLVAAYILDDCHMETYPKALVEKMIEAYESVNEDMDECFPDCPDGPEVLKSLSFVENVSARNIIATMMDYVNRSSLIVWHSGRVALDRAKDFRKRMAGTLRAYFDGVQMKDTEWSTWSVAQYLWSRCPESGAPCFYLSNEFFSGFLETTSSMPVLKFYDQYMYGSALCSVVNDLVSIYRDVNTDDVNITKILDKSCNIKETEEQIFVLLQLLETIIRFIYNSTKKMKKEYPACSSLFDFINDTSIGWIYIHTFTMRYMSSPDKVSITPLKEEMVNGWLNEKENESTVRNIQEFQSVLEKEREKMKRLYAF</t>
+  </si>
+  <si>
+    <t>SCB-144_TC1</t>
+  </si>
+  <si>
+    <t>MACSKPEVRFPMGWSKHHHDIGNEAVDEQLLAEDELIDWLIAIDLCNKSTVKKYIEKCRPYHFMRCVAAVVPNNLIFRDIFKTYMHLLVGVYYSDDKIETYNSTEIRQIRDSYEMLDGQVFEQFPTIAKMKASLKINKKLMPHVILMVDFLNNIEHSLIQQRTISEDNIAEYRRRISIANSMYFEAVEAEISCCVDDTTEMLWRRIFTGGAIHYLLGLEAMLGVIGKVKAHSTLITEMYVISALFCMLINDIYSYHKEVLSKAGDKGDNIIICMFEKKEVSEVPEAIQKIAQISNAIIKYMYQKVEKTKQEYPDNPDLHKLLDYIGMATVGWFFIHDSISCRYLDSPWRLSLVEVEEMELKEWRKGKDEEQSVVLQRFLYHSSPRGKTLIDALCGSIKTCGHFVPT</t>
   </si>
   <si>
     <t>BaTC-2</t>
@@ -155,6 +332,9 @@
     <t>MTKPFEVTAPTRWVKFHARVLSQPPIENFIRMEQLINWGVACGVTNEAGIRKSFQKLNAYVYLRCMYPLVADDAWSAEMFRINLHFTTAGYIVDDRIERYTMEEMNELCDGYDMLEKEVSKLFPKCPSIEEMRCRLQHLKNKFSIAAITMVMDFVNQSALFFLRQGKTSRDRVDNFRKRLSNAVTIYYQAVRNKVKTGCKITEGEMLWRRCFDVLAVPSYLAPESFTHAVEKQEWPLEMLYELYMLGILYSTVINDLYSYHREKLDDCDNVIKVWMQENSVSSIEEANEKICMILDAILQIMYEKIEKAKAQYSKCPELQRLLDYTGIVSAGWIFVHNTAAPRYLESPYQVVLREIEDKDIQGWLENKNEFGWRVVRHFMETMKSEKGKPVMDAMCGFTDARNILI*</t>
   </si>
   <si>
+    <t>klysimplexin R</t>
+  </si>
+  <si>
     <t>EcTPS-1</t>
   </si>
   <si>
@@ -174,186 +354,6 @@
   </si>
   <si>
     <t>MPSPYEVTAPASWVKDHKEVLPQPPIENLVRMEQLINWIVACGIADEATILDVYKKINAYVYLRCMYPVVPSDAWSAELFRINLRFTVAGYIIDDRIETYTMEEMNEICDGYDELEAEMSKMFPKCPSIQDMRNRLKHLKTKFSIATITMLTDFVNQFTLSYLRQGKTREDRVDNFRKRLSNSVSIFLQAIRNRVRIGSKITEGEMLWRRCLDVLAVTSYLVPESFTQAIDKDEWPIAVLYELYFLGILYSTVINDLYSYHRDKLDDCDNVIKVWMQDKTVSSIEDANEKICMILDAIIQIMYEKIEKTKAQYPNSPELQSLLDYTGFVSAGWIFVHNTVAPRYQEAPYTVVLKEIEEKDIQSWLEEKNDYGWSVLRRFLEFMKSEKGKPVMDAFCGFMDARNAAY</t>
-  </si>
-  <si>
-    <t>klysimplexin R</t>
-  </si>
-  <si>
-    <t>CiTC-1</t>
-  </si>
-  <si>
-    <t>MSCSKEVRFPETWSKVQWNCLKTPRDEDIFGFQELIKWLEDCGASDEANVRKYEEILNVYYATRAIIPIVPENILCRELCKVKIHFFMTTFVTDDLMEEHCSFEDMRKIIAALNQLNEKLSLEFKKVPSIKEMKKYLQYMSDERAISLVTVCMDFINRCTRTLLQHGNVSDDVVFDYRKRCFITVSLWLQGVAMVKRDGAAQDTVVDVLWTRVHDGLPSAFILYTEVSSFSLGKQNAHIAELTELYCLFGLYMVAINDFYSYTREMNDTIFSQSVIKIWLKNKEINNFSEAAPKMVAILDEISKYVYRKGEKMKAENPTNFELHEMVDQIGYGVAGNYFLHHHVCKRYKDTTAIKLGIKELKGKELKQWLAEKDPYGWDIVKNFLVDHSIVAKNFVDVMRGVTPLSDDSLLNSLNK*</t>
-  </si>
-  <si>
-    <t>DgTC-1</t>
-  </si>
-  <si>
-    <t>MWCGKEVRVPRQWAVLEQEVLKEKPDPELVDIDGMIKWITECDIVDENVVRAYVKLVKPYYFIRLIYPILPKDKLCVEACKIFLHFVISLYCSDDRTELECDLDDIVKMCDAYENLKEPVFEMFPKFPTIKEMQSSLKFLSDSKLISPVVLCMDFVNKVTSCVIEYGEYSETAVLDFRRRFLNTIEFYLRGLEMEKKMHRKDTENKTLWRRIFDGGPLFFLPYVEISSFSLGKVEGHIPTISEMYIVSAFVCIIVNDLYSYKRETMESINCDSVIKHWLSDEKISSMEEACEKVSRILNATVQYMFEKVQRVKLDYPNSPEAHVLYEYIAHVTIGWLYMHEEGNDRYKDSPWRVSLTEVEEDKIQEWLSCKDSYGFEALNQFLASNPKAEKIIDALGGDEIIHGGLINESS*</t>
-  </si>
-  <si>
-    <t>HcTC-2</t>
-  </si>
-  <si>
-    <t>MACSKEMYIPKEWTKYHHDIVKEVKRADLEADDEVAKWVVGLGLSDKPATEKYIDSTRPYHFMRCIAVLVPSNPLCRNIFKTWQIYVTGLFVSDDYLEQTSLAEVVQVSDSFDMLNEQISERFPVIPTHAQIMRSLKINEKLIPHVLVQIDWLNTIANDLLQHGDFSEDDVWDFRCRMSAWIRAYFDGLKSQVGPKVKVTTDDFMWLRIIDGGVGPFLLINEILVGELGKCKGHVKLITQLYILSSCVCVLINDCYSYHRETVVTIYNTIKVILENKEVSEVPDAVSKLLQTINAIIKYMYQTIEKTKHEYPDNLMLNKLLDAIGGATAGWFFVHDKVLPRYQATSWRFSLVEVEEMELKEWRKSADEKPSDLVQPLLYRFNAKGKEIIDALAYVPKRSRRIVPE*</t>
-  </si>
-  <si>
-    <t>TmTC-2</t>
-  </si>
-  <si>
-    <t>MSCSKEIRIPSDWASVQRKSMQEGPDESLLDFEELANWLRECGVTDDQCKVRKYVDATRPVLSIRTILRVFPNNTLCRMHFKFLTQYTIGIYIDDDVLESHYPLEVLKEICYEYDQLDGKLLGQFPQIPSRKELKNFLAHLKNEKVISTVTFHMDFVNRVTVNILQNGDFSEEAVLEFRRRLSNNILLYLQGVQYEKRGAGGKPSTVVEALWNRVFGGAAVTWRLFGEVPSGTLGKIGEHITLISELYILSALYCIVINDLYSYHREIDAVPTAGENFVRVMFNQKEVANLTVAAGKVASILNEITKYTYEQVREFKASYPNSSELHQLFDDIGCGTVGWYYFHECTNPRYKESNVRISMKDVDKNEIEDWLSTKDSYGWNIVKQFLASYDAKAKRLNDAVACRIPAYAETF*</t>
-  </si>
-  <si>
-    <t>PcTS-2</t>
-  </si>
-  <si>
-    <t>MSCSNEVRIPSNWAFLEKEVLKEQPDPELVDIDGLIKWVVECEIADENMVRKYVKIVRPYYFARLLYPILPNNRLCREAFKIFLHFVIAVYRCDDRMETECDLNDMGKICNAYDKLDEQLCETFPKIPTVKEMQSSLKFLSEAKLIAPVTLCMDFVNKVTCAILTHGSVSEDVVFEFRRRLSNSVSIYLKAVKSEKNMTPEDSDNETLWRRIFGGGPLFLLLYVEISSFSLGKTKEFIPTITEMYVVSSLCCIITNDVYSYYRETTESLIYCDSIIKVWLHNKEITTIPEAIARITNILNATVKYMFEMGKNVKIQYPNSPEVHALFEYIAYATIGWMFMHDQGSHRYRDSPWRISLVDVKEIDLQQNKDSYGEDVLKTFLEMSNSKAKKIIDALRGVIAVREDLIYDNC</t>
-  </si>
-  <si>
-    <t>NA-218_TC-2</t>
-  </si>
-  <si>
-    <t>MWRTDVVKVPRKWVQPHKELLKNKRNHEHLIVEEMYQEVYEIGLTTEEKVREIIVNINAGTYARFLFPDFLDNPESNKVPQLMIYYVTVLYLIDDQLETFNETEIEELIDGYNQLEREMFETFPKCANMTKMKTMLRNVKNEFTKSSIVMMMDIVFKATSLYLEQRQPPHEKMLDFRNRFSAQLSLFNYAHLSRAKYGTNATPGEMMWRRCTDSLMFALPMAIEMLDKTSEKEVPTMREIYELYTMSVLYGVVINDLYSYFREQFDCSNNLLKVLFPKKVDPNMTDATVKICQILNAIMKHAYFLVEKLKLKYPHAKNLLDDNAYQISSWIYIHATVAPRYYTSPCHVEVVEIEDGELSDWLTQENEYGSRVFQEFLDIMNDPTQKSARDFFHGTDVDRQFSI</t>
-  </si>
-  <si>
-    <t>SCB-144_TC4</t>
-  </si>
-  <si>
-    <t>MAYSKPIHAPREWVKDVKEVLTPALVDEELLGLDELVAWALECGICNEKLVKKYAKYISPYLLIRGLYPVLPNNTLCRSVFTIFVHFTLLLYIADDRMEKQSEEEGRNMCVGFTLLDEQSRKSFPEFPTVEEMKATIIHMSTPSIVGRTVMLASFVDKLASALLKHGNYSDDVVYDYRLRASNMLSIYIQALLAEKHQQKQGTVLEAFWRRHFGGCVIIFHLLADIFSGALGKTKHHLAVITDLYINCTLLCIAINDLFSYFLEKESSCDNIFREILAEKEEENIPEAVHKMSQIADAILKRLYRTMQETLQQYPKHQELRSLMGYVGRCAVGWFWMHSILQRYMDSPFKFTLDEVDDEHLMTWSSKNNDYGENVVNDLMKMFKERMADGKMDALKGAFPIHEKISGYKEDGLYNVV</t>
-  </si>
-  <si>
-    <t>SCB-157_TC5</t>
-  </si>
-  <si>
-    <t>MAYSKPIHAPSVWVKHVKEVFTPASSVDEELLGLDELVGWALECEICDEEMVKKYVKSITPYRFMRALYPVFPDNILCRSVFKVLAHYVILLYIADDKMEQQSEEEMRNMCVGFTLFDEQSRKSFPELPTVEEMKMTINHLSTPGTVGCTVMFASVANKMASALLKHGNYPDDVVYDYRLRASNMLSIYIQAILAEKHQQKHGTVLETYWRRQFGGCVLIYHLLADISSGALGKTKQHLGVITEMYIYCTLLCIAINDLYSYSFEKETICDNIFKAILEEKQEENIPEAVDKISQIADAILKRLYRKIQETLQKYPNNQELRSLMDYLGRCAIGWFWLHSILQRYKDTPFKLTLVEVDDEHLMTWSSKNDDYGENVVNDIMKMIKERMADGKMDAMMGAFPIHEKISAYKEDGLYNVV</t>
-  </si>
-  <si>
-    <t>NA-195_TC-1</t>
-  </si>
-  <si>
-    <t>MSCSKEIRMPKKWSKYHHDIMKKTVNEEIFNEDECMNWFAACGVSDKSCIKKYIEAIRPYHFTLCLAGFIATSHRDVMRSYMYYLIGVYYVDDCLESHSSSEVHQVGEAYAKLEKQVWEQYPQFSTIPEMKQYLKERVEIDETLIHHVVILFESLSKITNALLQHGQLNQNDVRNFSRRLSNSITMFLEAVEAESTPSITANSTYHEILWRRIEGGAPMMFINVVEITAESIGKVKEHTTCITELYVLSSLFVIFLNDLYSSYKEKIEKIDCDNVVHSLIANKDALHVLDAAEKITPIMNGIIKLMYQKIEKIKCEYPNNPDLHKLLDYIGVGTAGWYTIHAECSPRYFASTSCRIPLVEVEEKELEQWKKDHDQLSFDEPGVSIESYLYHSNTKAKTMIDAHSGRISPRGHFIPV</t>
-  </si>
-  <si>
-    <t>SCB-157_TC2</t>
-  </si>
-  <si>
-    <t>MAYSKPEVHFPKEWTKHHHVIGKETVNEELFPEDELVDWLTSIDMCEKSTIQKYIEMCRPYHFIRCLAVLVPIHLSSCRDLFKIYVQFVIAIFISDDLLETYNSTELRQIRDSYEMLEGQVSAESFLPFPTIAKMKASLKIKKKLMPNVIYLVDCTNMVAHSLIQQGTISEDDVAYFRKRISIAHSMYLEAVEAEMSPRVDETITEILWRRIFNGALPGILLGVEAMSGMVGKVKPHALLIAEMEILCSLYCILINDIYSYGKELLSKVGNKDTKCDNIVVSMLHNKEVSSISEAVQKIFPVCNEVTKYMYQKIEKSKQEYPDNEDLHKLLDHIGRATAGWFFIHDSVLPRYEDTPCVISLVEVEEMELKEWRESKDEEQSVILKRFFDHTSPKGKILMDAMCGLIKTRGHFVPT</t>
-  </si>
-  <si>
-    <t>NA-047_TC4</t>
-  </si>
-  <si>
-    <t>MACSKELRIPKPWLKYHDAIVKEPVDPKLFSLDELCAWLKDLDLCHNKSDVAKYVLQTRPYHLVRHQVVLLPDNALCRELFTLWVNTAVALYISDDVLELLSDIEMRQICDACQLLDDHIREQFPQFPTIAEMKQFLLVQKLDEKLIPHVIYFQDFSNNVAKAIMEHSNFSKEEVKYFWRRLVVKIALYYEGVGDEGKHTIGLYSKNVWTRLLAAGVMIWVFSLEIMFGVVGKTTQHLPLLNELYFIATFLAMVVNDIYSYKREMGLDARVCNIVQTIIVGEEASGESQAVQKCVEMLNAVVKVSYQKIERAKQENPGDQDLWKLLDNIGMATVGWYFCQHFSPRYDDSPWRLSIVEVEGAELEEWRHTDEDPPKEVIPLLVSYNAKAKRISDAIISGDVNMHGNL</t>
-  </si>
-  <si>
-    <t>SCB-084_TC1</t>
-  </si>
-  <si>
-    <t>MSCSKEVQFPSNWAKVQWHYLRKPKDEGLIGLEELINWAEECGIADEITVRKYVEVVKPYKTYRSVCPIVPDNTLCRGLFKTCMQFMLVLFILDDVFEKNCNLDDMEKIINAYHQLDEKLSETFPKVPSIKELQPYLQYLSDKRINSIITFLMDYVNRSVRVLLQHGNVSDDAVLDYRQRLSNGMSLYLQGIASEKRDTTQDSENKVLWRRMFDGALHILISYIEASSFSLGKQKAHITAITELYTLFSLYCVVINDLYSYTRESNESVPSTNVIKVWLNKKEIANISESARKVVSILDEITKYVYKRVEKMKVENPNNSELHELLDQIGYAIAGNYFFHHYASDRYKDAQIKLGMKEVEENELQEWLAERDPYGWDVVKQFLNEHSTVAKNFTEILCGVTPRSVDSLLSLLSK</t>
-  </si>
-  <si>
-    <t>SCB-084_TC6</t>
-  </si>
-  <si>
-    <t>MSCSKEVQFPSNWAKVQWHYLRKPKDESLLGLEELIKWVEECGTGDEITVRKYVEKLKPYEGMRAFCPIVPDNNVCRGVFKIYVQYILGVFIIDDVMEKNYNLDYMMKIINAYDQLDEKLSEIFPKVPSIKELQPFLQYLSDKRIRSIVTFYMDFVNRCTRVLLQDGNVSDDAIFDFRQRLAIGISLYLQGAASEKRNTTQHTEIEVLWRRVFDGMPIPFVQYVEVSSFSLGKQKAHVAAITELYTLFSLYCVVINDLYSYTREDNESVPAASVIKLWLDKKKIGNISESVPKIISILDEIAKYVYKRVEKMKVENPNNSELHELLDQIGYSIAGNYFFHHHASDRYKDAEVKLGMREVEENELQEWLADNDPYGWDVVKQFLYEHSTVAKNFIDISCGVTPRSVDSLLSLLSK</t>
-  </si>
-  <si>
-    <t>SCB-084_TC2</t>
-  </si>
-  <si>
-    <t>MSCSKAVRFPSNWARVQWHYLRKPKDEGLIGLEELIKWLRDECGAADESTILKYVKNVKPYESMRAFCPIVPDNNVCRVVFKIYVHFILGLFIIDDVMEKDCNPDDMEKIVNAFDQLDKKLSEAFPKILSIKEMQPFLQYLSDKRASSIVTFFLDFLNRCARVLLQDGSVSDDAIFDYRQRLAHAISLYLQGAASEKRDATQDTLHKVLWRRLHDGAPIPFLQYVEVSSFSLGKINKAHIAAATELYVLFALYCVLINDIYSYTRESNESLPTTNLVLVWLKKKEIGNLSESIPKIISILDEIAKYVYKRVEKIKAENPNNSELHELFDEIGYGIAGNYFFHEHASDRYKDSEVKLAIKELEENDLQDWLADSDPYASDVVKQFLLEHSTVSVAKNFNDLLCGVTPLSVDSVLSLLNE</t>
-  </si>
-  <si>
-    <t>NA-045_TC-1</t>
-  </si>
-  <si>
-    <t>MSCSNEVRIPSDWAFLEKEVLKEQPDPELVDIDGLIKWVVECEIADESMVRKYVKIVRPYYFARLLYPILPNNRLCREAFKVFLHFVIAVYRCDDRMETECDRDDMEKICNAYDKLDERLCETFPKIPTVKEMQSSLKFLSEAKLIAPVTLCMDFVNKVTCAILTHGSVSEQVVFEFRRRLSNSVSIYLKAVKSEKNMTPEDSDNETLWRRIFGGGPLFLLLYVEISSFSLGKTNAFIPTITEMYVVSSLCCIITNDVYSYYRETTESLIYCDSIIKVWLHNKEITTIPEAIARITNILNATVKYMFDMVKNVKIQYPNSPEVHALFEYIAYATIGWMFMHDQGSHRYKDSPWRISLVDVKEQDLQQNKDSYGEDVLKTFLGMSNSKAKNIIDALRGVISVREDLIYDNQ</t>
-  </si>
-  <si>
-    <t>Sesquiterpenes</t>
-  </si>
-  <si>
-    <t>XsTC-1</t>
-  </si>
-  <si>
-    <t>MSEKNVVRIPMKWGRIEREILTQNTIPELVDTNRLISWVKECNLADEALVTKYMNVIRPYHFSRLVFPILPDKDVCREAFAVFIEFLIVLYLCDDELEAKCNLNELEIVCSAYDFLDEKLKQCFPRIPSVEELRSFLPHVKKERLLALVVSLIDSVSRVVSPLLKYSVFPQESVFDFRCRFSHSLGYNLKGVLHEKKMLGGVSENKLLWRRIFEGAPITFLMYLEISSLSVTGSNKHIPIATEMYILSSLCCMVTNDVYSYHRECNEGLKVDNIISLWLHNKQIASVAEGVSRISRILNSAVKYMLAKVKSMKSEYPNNFNVQTLTEFIALSSVGWLYMHDQGVPRYSDSPWRLNLVDIEESDITSWLAEKDPYADGVIDQFKYSNLDAKKFIDSLCEKTSVSEEQWND*</t>
-  </si>
-  <si>
-    <t>NA-045_TC-5</t>
-  </si>
-  <si>
-    <t>MACSKHIRIPATWLYPHQKILQDAPKADSEAPKEMVDWLCYEVKLADEALVNHTFHHLKPYLFVSLMYPRLPSDPWSKKLFELNVYFLVAAYILDDYHMENYPTTLIEKMLAAFNSVNKDMDECFPNCPTGTEIVQSLSYVENPSARYIIATMTDYINRSALIVWNSGRVQLSRAQDFRKRMAGTLRAYFHGVQMKGRHWTALSVSQFLWERCPESGAPCYYLSNEFFSGFLETTSSFPLAMLYDHYMYGSAVCSVVNDLVSLDRDTSSGDVNIIKILDKTGKIEDMEVAKSAILQLLESLVRYIYNSTKQMKEEYPECSSWFDFINDMTTGWICIHMFSPRYASSPNKVFMTPLHGEALDEWLNEKENASTFTDILAFQKLLDEMRDKMKMLYAF</t>
-  </si>
-  <si>
-    <t>NA-195_TC-3</t>
-  </si>
-  <si>
-    <t>MACSKHVRIPATWLYPHAEVLRDPPKEDSTTPKELVTWLSHEVKLADEDMVDKTFHHLKPFFFVSLMYPRMPTDPWCLKLYELNVYFLVAAYILDDCHMETYPKALVEKMIEAYESVNEDMDECFPDCPDGPEVLKSLSFVENVSARNIIATMMDYVNRSSLIVWHSGRVALDRAKDFRKRMAGTLRAYFDGVQMKDTEWSTWSVAQYLWSRCPESGAPCFYLSNEFFSGFLETTSSMPVLKFYDQYMYGSALCSVVNDLVSIYRDVNTDDVNITKILDKSCNIKETEEQIFVLLQLLETIIRFIYNSTKKMKKEYPACSSLFDFINDTSIGWIYIHTFTMRYMSSPDKVSITPLKEEMVNGWLNEKENESTVRNIQEFQSVLEKEREKMKRLYAF</t>
-  </si>
-  <si>
-    <t>SCB-144_TC1</t>
-  </si>
-  <si>
-    <t>MACSKPEVRFPMGWSKHHHDIGNEAVDEQLLAEDELIDWLIAIDLCNKSTVKKYIEKCRPYHFMRCVAAVVPNNLIFRDIFKTYMHLLVGVYYSDDKIETYNSTEIRQIRDSYEMLDGQVFEQFPTIAKMKASLKINKKLMPHVILMVDFLNNIEHSLIQQRTISEDNIAEYRRRISIANSMYFEAVEAEISCCVDDTTEMLWRRIFTGGAIHYLLGLEAMLGVIGKVKAHSTLITEMYVISALFCMLINDIYSYHKEVLSKAGDKGDNIIICMFEKKEVSEVPEAIQKIAQISNAIIKYMYQKVEKTKQEYPDNPDLHKLLDYIGMATVGWFFIHDSISCRYLDSPWRLSLVEVEEMELKEWRKGKDEEQSVVLQRFLYHSSPRGKTLIDALCGSIKTCGHFVPT</t>
-  </si>
-  <si>
-    <t>Protein</t>
-  </si>
-  <si>
-    <t>HcTC-3</t>
-  </si>
-  <si>
-    <t>PbTC-1</t>
-  </si>
-  <si>
-    <t>PcTS-1</t>
-  </si>
-  <si>
-    <t>AbTPS</t>
-  </si>
-  <si>
-    <t>AeTPS</t>
-  </si>
-  <si>
-    <t>RhTPS</t>
-  </si>
-  <si>
-    <t>AaTPS</t>
-  </si>
-  <si>
-    <t>SCB-144_TC3</t>
-  </si>
-  <si>
-    <t>NA-045_TC-3</t>
-  </si>
-  <si>
-    <t>MSCSKEVRAPRKWVQRQREMQKVKVDDNLISMDELIELVVECGLCDEASVHKMYERTNTYQFMWTLIPTVPSDQWQFEIFKTSLHFLCALFLVDDAVESYSEKQMKEMSDAYDMLEKQVCENFPCFPSINEMKQSLKHLKNPFDIASITFCMHYVNKIASVLVNEGSTPQNVVYNFRRRTSNAISISFQAVLIKAKLGSNVTGDEMLWRRVYDGLVILFYQFGELVLGLTKNTEKYMTVITELRLLGCLYCIVINDLYSYHRDKLVSSDNIIKTWLLGKAVSNLSEASSRCCEILDAVMQYMHERVERIRQSHPGCPELEALLETTVYTTVGWIFAHTAVVPRYSESPLKVHLVEVEESELHTWFCEKNHYGRSVIEKFLKAVNDEKHKGILDALSGFVDGRGQLLKTQL*</t>
-  </si>
-  <si>
-    <t>MSCSKEIHAPRRWVDRHKQIPVLPQNAVEKLISMNELIELVIECGLCDKTSINKMYDKINTYQFMWCIVDTVPASQYAEEIFKSSLHFLCALFLVDDAVESYSANEMQDLSRSYDTLEKEVCKTFPNFPSINEMKESLMHLRNPFDRSSITFCMQYVNKITAILLEEGNTPHHVVYNLRRRTSNAISIAFQAVLIKSKCGSIITSHEMLWRRVFDGLVILFYQFGELISGATETAQQHIAVVTELRMLGCLYCIVINDLYSYQRDKLASSDNMIKTWLLEKTVSSLSEATARCSQILDAIMKYMYQRVEQCIQSNPGCPQLESLLETTIYTTVGWIRSHTTVVPRYSESQLKVALVEVEEKELPKWLAEKDEYGWNVVEKFVETLNDEKHKGLLDALQGIADGRDQLLKTQLDIS*</t>
-  </si>
-  <si>
-    <t>MSCSKEIHAPRRWVERHKQVQVLPQNAVEKLISMNELIELVIECGLCDKTSIKKMYDKINTYQFMWCIVDTIPASQYAEEIFKSSLHFLCALFLVDDAVESYSANEMQDLSRSYDILEKEVCKTFPNFPSINEMKESLMHLRNPFDRSSITFCMQYVNKITAILLEEGNTPHHVVYNLRRRTSNAISIAFQAVLIKSKCGSIITSHEMLWRRVFDGLVILFYQFGELISGATETAQQHITVVTELRMLGCLYCIVINDLYSYQRDKLASSDNMIKTWLLEKTVSSLSEATARCSQILDAIMKYMYQRVEQCMQSNPGCPQLESLLETTIYTTVGWIRSHTTVVPRYSESQLKVALVEVEERELPKWLAEKDEYGWNVVEKFVETLNDEKHKGILDALQGIADGRDQLLKTQLDIS</t>
-  </si>
-  <si>
-    <t>MSCSKEIYVPRRWVQRHKKIPVLAQPAIEKLISMNELIELVIECGLCDKTSISKMHEKINTYQFMWCMVDTVPASQYAEEIFKSSLHFLCALFLVDDAVESYSAKEMQDLSRSYDILEQQVCKTFPNFPSINEMNESLVHLRKPFDRASITFCMQYVNKITAILLKEGNTPHDVVYNLRRRTSNAISIAFQAVLIKSKCGSIITSDEMLWRRVFDGLVILFYQFGELISGTTEIAQQHIPVLTELRMLGCLHCIVINDLYSYQRDKPALSDNIIKTWLLEKSVSSLLEATARCGQILDSIMKYMYQRVEQCKQSNPSCSQLKSLLETTIYTTVGWIRSHATVVPRYCESQLKVSLVEVEEGEIPKWLAKRDEYGWNVVEKFVETLNDEKHKGILNALQGIVDGRDQLLKTQLDMHDDVV*</t>
-  </si>
-  <si>
-    <t>MSCSKEIYVPRKWAQRHEKIPVLAQTTIEKLISMNELIELVIECGLCDKTCISKMYERINTYQFMWCMVDTVPASQYAEELFKISLHFLCALFLVDDAVESYSANEMWDMSRSYDALEQQVCKTYPNFPSISEMKESLVHLPNPFDRASITFCMQYVNKITAILLKEGNTPNDVVYNLRRRTSNAISIAFQAVLIKSKCGSTVTSHEMLWRRVFDGLVILFYQFDELISGTTEIAQQHIPVLTELRMLGCLYCIVINDLYSYQRDKLALSDNIVKTWLLQKSVSSLSEATARCGQILDSIMKYMYQRVEQCKQSNPSCPQLKSLLETTIFTTVGWIRSHTTVVPRYSESQLKVSLVEVEEEEIPKWLTKRDEYGWNVVETFVENLNDEKHKGLLDALQGIVDGRDQLLKTQLDMHDDIM*</t>
-  </si>
-  <si>
-    <t>MPFSKHIHVPSHWLDGQKAMLNKERDETLISMEKLIDLVTECGLCDEASIRKIDKKINTLQFMWTLVDTSPSDQWSTEIFINCSHFLCAAFLIDDAVESYSAVEMEKLSNAYDLLEQQSCEAFPNFPSICEMKKSLEGLMLNVFDIASVTFCMQYVNKIASILLKQGNTRNNLAFNVRRRTSNAISISLQAVLVKSKHGSKVAPHEMLWRRIFDGLVILFYQFGELTSGVTKHVQQHIAIVTELRMLGCLYCVVLNDLYSYHRDKFAPSDSIIKTWFTNKTVSSLSEATTKCCQILDAVLKYMYERVEECKLRFPDSPELKVLLESTVYTTVGWIFSHTIIVPRYAESPLKVILVEVEKLELAAWLAQKDEYGCNVVEEFIKTMNNKENKGIIDALSGCVEGRGQLVKTLVSDQ*</t>
-  </si>
-  <si>
-    <t>MACSKQLRVPKQWLKYHDDIFKEPVNSKLFSEDELCVWLKDLDLCHNKSVIAKYVQTTKPYHLMRHQIVLLPSNALCEKIFTLWTNTIIALFIGDDVLETLNKAEMGEICDAFQLLDEHTHDQFPQIPTIAEMRQFLMQQKVNEKFIPHVIYFQDFSNNVVKCMLEHGNSSKEDVKDFWRRLVVMIAFYYEGVEDEVKSSVGVYADDVWKRSLSSAAMVWMIAQEITSEVIGKTTVHAPLLNELYFLGTFYSMVVNDIYSYKREMLLEASVCNLVQTFTVSKVVPGESEAVQKCVDILNEVVKVMYQKIEKVKQENAGDQDLCKLFDNIGMATVGWYYFHHYSPRYDDSLWRLPIVPVEDDELKEWRQCTDKDPMEEVMALLIKYCEKAKRISDAIIGGKVNMHTNL*</t>
-  </si>
-  <si>
-    <t>MSCSKPIHVPSHWVNRQKAMLNKKTDETLISMEKLIDLVTECGLCDEASIRKIDKKINTFQFMWSLVDTSPSDQWSREMFTNCFQFLCAAFLIDDVVERYSAVEMEELSDAYDFLEQQSCEAFPNFPSISDMKKSLEGLMSNVFSIGSVTFGIQYVNKMASILLKQGSTPENVVFNARRRTSNAISISLQAILIKSKHGSNVAPHEMLWRRIFDGLVILFYEYGELVSGVTKHVQEHVAIVTELRMLGCLYAVVINDLYSYHREKHVPSESIIKTWFSQKIVSSLSEATTKCCQILDAILQYMYERVEECKLRFPECPELEVLLESTMYTTVGWIFSHEIIVPRYSESPLKVILVEVANEEVPAWLAQRDEYGWNVVEQFVKTMNNKENKGIIDALSGYVEGRGQLIKTLDK</t>
-  </si>
-  <si>
-    <t>MSCSKEIHVPRRWAERHKQIPVLPQNTVEKLVSMNELIELVIECGLCDKSSINKMYDKINTYQFMWCIVDTVPASQYAEEIFKSSLHFLCALFLVDDAVESYSANEMKDLSRSYDTLEKEVCKTFPNFPSINEMKESLMHLRNPFDRSSITFCMQYVNKITAILLKEGKTPHHVVYNLRRRTSNAISVAFQAVLIKSKCGSIITSHEMLWRRVFDGLVILFYQFGELISCATETAQKHITVVTELRMLGCLYCIVINDLYSYQRDKLTSSDNMIKTWLLEKTVSSLSEATARCSQILDAIMKYMYQRVEQCIQSNPGCPQLESLLETTIYTTVGWIRSHTTIVPRYSESLLKLAPVEVEENELPKWLAEKDEHGWNVVEKFVETLNDEKHKGILDALKGIADGRDQLLKTQLDIS</t>
-  </si>
-  <si>
-    <t>elisabethatriene</t>
   </si>
 </sst>
 </file>
@@ -713,13 +713,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -730,10 +730,10 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -744,10 +744,10 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -758,10 +758,10 @@
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -772,10 +772,10 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -786,10 +786,10 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -800,10 +800,10 @@
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -814,10 +814,10 @@
         <v>14</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -828,10 +828,10 @@
         <v>4</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -842,10 +842,10 @@
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -856,94 +856,94 @@
         <v>19</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="C14" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="C16" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -954,458 +954,458 @@
         <v>39</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>48</v>
+      <c r="A23" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>50</v>
+      <c r="A24" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
-        <v>92</v>
+      <c r="A46" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>104</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
